--- a/Stats Sheet/Round Gaps/WMC.xlsx
+++ b/Stats Sheet/Round Gaps/WMC.xlsx
@@ -661,7 +661,7 @@
     <x:t>KirbyMD</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>Ninjajaja</x:t>
